--- a/assets/constructions/examples/ctd_mib_cartmill1.xlsx
+++ b/assets/constructions/examples/ctd_mib_cartmill1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,11 +584,31 @@
           <t>cartcount</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MT260K-160C40R08SN12</t>
+          <t>MT290K-100A32R06SO12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,39 +618,39 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>63</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>4000</v>
+        <v>1600</v>
       </c>
       <c r="N2" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>SNGQ1207DNT + SNGQ1207DNTR</t>
+          <t>SO.T120408.N...</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -638,12 +658,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ISO_6462:SPK01040</t>
+          <t>ISO_6462:FDAxx032</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>SKIF_SN1207H</t>
+          <t>SKIF_SO1204H</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -658,7 +678,7 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>SKIF_SN1207H</t>
+          <t>SKIF_SO1204H</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -669,13 +689,19 @@
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT200K-200C60R12RD16</t>
+          <t>MT200K-100A32R06RD16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -685,47 +711,43 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>63</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="N3" t="n">
-        <v>9.9</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>RDNT1605..</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ISO_6462:SPK02060</t>
+          <t>ISO_6462:FDAxx032</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -756,13 +778,19 @@
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>12</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT245K-160C40R10SN13</t>
+          <t>MT260K-500D60R22SN12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -772,39 +800,39 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>60.8</v>
       </c>
       <c r="O4" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>SNMU1306ANSR-F</t>
+          <t>SNGQ1207DNT + SNGQ1207DNTR</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -812,12 +840,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ISO_6462:SPK01040</t>
+          <t>ISO_6462:SPK05060</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ISO_SN1306H</t>
+          <t>SKIF_SN1207H</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -832,7 +860,7 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>ISO_SN1306H</t>
+          <t>SKIF_SN1207H</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -843,13 +871,19 @@
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>10</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT290K-100A32R05SO12</t>
+          <t>MT260K-400D60R26SN12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,39 +893,39 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>39.6</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SO.T120408.N...</t>
+          <t>SNGQ1207DNT + SNGQ1207DNTR</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -899,12 +933,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:SPK05060</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SKIF_SO1204H</t>
+          <t>SKIF_SN1207H</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -919,7 +953,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>SKIF_SO1204H</t>
+          <t>SKIF_SN1207H</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -930,13 +964,19 @@
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>5</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT200K-125A40R08RD16</t>
+          <t>MT200K-160C40R08RD20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -946,7 +986,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
@@ -967,27 +1007,31 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>RDN.2006MO..N</t>
+        </is>
+      </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx040</t>
+          <t>ISO_6462:SPK01040</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SKIF_RD1605H</t>
+          <t>SKIF_RD2006H</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1002,7 +1046,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>SKIF_RD1605H</t>
+          <t>SKIF_RD2006H</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1015,6 +1059,12 @@
       <c r="AE6" t="n">
         <v>8</v>
       </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
